--- a/SuppXLS/Scen_UC_ELC_MANHEAT_30_50.xlsx
+++ b/SuppXLS/Scen_UC_ELC_MANHEAT_30_50.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E27BEB50-F499-422C-9525-EF2ABD4AC0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC8A00A8-0478-4043-804E-6CE8130260EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
   </bookViews>
   <sheets>
-    <sheet name="ELC_MANHEAT_10_20" sheetId="1" r:id="rId1"/>
+    <sheet name="ELC_MANHEAT_30_50" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
